--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536314_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536314_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,64 +1633,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2424</v>
+        <v>2.7324</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2424</v>
+        <v>3.4616</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2424</v>
+        <v>3.8851</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8753</v>
+        <v>-0.4381</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3671</v>
+        <v>4.3232</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2424</v>
+        <v>5.8063</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8753</v>
+        <v>0.2825</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3671</v>
+        <v>5.5238</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-1.9212</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.7206</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-1.2006</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.0822</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.0274</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0.4062</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.5707</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.1645</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.3082</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.3082</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CARREÑO VIDAL</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5918</v>
+        <v>-0.4107</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5918</v>
+        <v>1.4279</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-1.8386</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5918</v>
+        <v>-2.149</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.485</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5918</v>
+        <v>-1.6641</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5918</v>
+        <v>0.6236</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.6614</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5918</v>
+        <v>-0.0377</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-2.7726</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.1463</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.6263</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.0274</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.0274</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.4671</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.6135</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.1464</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1781</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,64 +1965,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4107</v>
+        <v>-2.4896</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4279</v>
+        <v>-1.2187</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8386</v>
+        <v>-1.2709</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.149</v>
+        <v>-1.4194</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.485</v>
+        <v>-1.0172</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6641</v>
+        <v>-0.4022</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6236</v>
+        <v>0.4858</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6614</v>
+        <v>-0.7383</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0377</v>
+        <v>1.2242</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7726</v>
+        <v>-1.9053</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1463</v>
+        <v>-0.2789</v>
       </c>
       <c r="O19" t="n">
         <v>-1.6263</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0274</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0274</v>
+        <v>0.8219</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4671</v>
+        <v>-0.6249</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6135</v>
+        <v>-0.6771</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1464</v>
+        <v>0.0521</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1781</v>
+        <v>-0.2397</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4178</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-0.2397</v>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. COSTA I VAZQUEZ</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5101</v>
+        <v>-2.6278</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2192</v>
+        <v>-3.8511</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7292999999999999</v>
+        <v>1.2233</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6427</v>
+        <v>-2.3427</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3134</v>
+        <v>-1.317</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9561</v>
+        <v>-1.0257</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5639</v>
+        <v>-2.5832</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5929</v>
+        <v>-1.3219</v>
       </c>
       <c r="L20" t="n">
-        <v>3.1567</v>
+        <v>-1.2613</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9212</v>
+        <v>0.2405</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7206</v>
+        <v>0.0049</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2006</v>
+        <v>0.2356</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0548</v>
+        <v>-0.411</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0822</v>
+        <v>-1.0274</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0274</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4062</v>
+        <v>-0.1138</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5707</v>
+        <v>-0.72</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1645</v>
+        <v>0.6061</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3082</v>
+        <v>0.2397</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3082</v>
+        <v>0.4794</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>K. KELIKI EBENGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4896</v>
+        <v>-2.9955</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2187</v>
+        <v>-1.647</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2709</v>
+        <v>-1.3485</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4194</v>
+        <v>-1.2512</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0172</v>
+        <v>-1.3926</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4022</v>
+        <v>0.1413</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4858</v>
+        <v>-0.5723</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7383</v>
+        <v>-0.6512</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2242</v>
+        <v>0.0789</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9053</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2789</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6263</v>
+        <v>0.0624</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2055</v>
+        <v>-0.8219</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0274</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8219</v>
+        <v>0.2055</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6249</v>
+        <v>0.2557</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6771</v>
+        <v>-0.0473</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0521</v>
+        <v>0.3031</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2397</v>
+        <v>-1.1781</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2397</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6278</v>
+        <v>-3.0472</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8511</v>
+        <v>0.0157</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2233</v>
+        <v>-3.0629</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3427</v>
+        <v>-2.6408</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.317</v>
+        <v>0.6649</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0257</v>
+        <v>-3.3057</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5832</v>
+        <v>0.579</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3219</v>
+        <v>1.7219</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2613</v>
+        <v>-1.143</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2405</v>
+        <v>-3.2198</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0049</v>
+        <v>-1.057</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2356</v>
+        <v>-2.1628</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.411</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0.6163999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1138</v>
+        <v>0.1552</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.72</v>
+        <v>-0.5633</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6061</v>
+        <v>0.7185</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2397</v>
+        <v>-1.1781</v>
       </c>
       <c r="W22" t="n">
-        <v>0.4794</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2397</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. KELIKI EBENGO</t>
+          <t>P. CARRENO VIDAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9955</v>
+        <v>-4.1148</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.647</v>
+        <v>-1.782</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3485</v>
+        <v>-2.3328</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2512</v>
+        <v>-2.7202</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3926</v>
+        <v>-2.878</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1413</v>
+        <v>0.1578</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5723</v>
+        <v>-0.2626</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6512</v>
+        <v>-2.1574</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0789</v>
+        <v>1.8948</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-2.4576</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.7206</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0624</v>
+        <v>-1.737</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.8219</v>
+        <v>-2.0548</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0274</v>
+        <v>-3.0822</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2055</v>
+        <v>1.0274</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2557</v>
+        <v>-0.1685</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0473</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3031</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1781</v>
+        <v>0.8288</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.6575</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1781</v>
+        <v>-0.8288</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,235 +2380,69 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0472</v>
+        <v>1.0025</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0157</v>
+        <v>6.436199999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0629</v>
+        <v>-5.4338</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.6408</v>
+        <v>1.578000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6649</v>
+        <v>-4.496</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.3057</v>
+        <v>6.0738</v>
       </c>
       <c r="J24" t="n">
-        <v>0.579</v>
+        <v>12.6637</v>
       </c>
       <c r="K24" t="n">
-        <v>1.7219</v>
+        <v>-0.9175000000000004</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.143</v>
+        <v>13.5812</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2198</v>
+        <v>-11.0858</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.057</v>
+        <v>-3.5784</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1628</v>
+        <v>-7.5072</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6163999999999999</v>
+        <v>-2.0549</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-10.274</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6163999999999999</v>
+        <v>8.219099999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1552</v>
+        <v>-1.0274</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5633</v>
+        <v>-4.960100000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7185</v>
+        <v>3.9326</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1781</v>
+        <v>2.5068</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>9.006600000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1781</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536314_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>P. CARRENO VIDAL</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>TQ-CB PRAT</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-4.7066</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-2.3738</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-2.3328</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-3.312</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-2.878</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-0.434</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-0.8544</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-2.1574</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.3031</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-2.4576</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-0.7206</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-1.737</v>
-      </c>
-      <c r="P25" t="n">
-        <v>-2.0548</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-3.0822</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.0274</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-0.1685</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-0.09470000000000001</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.07389999999999999</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.8288</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.6575</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-0.8288</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536314_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>TQ-CB PRAT</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.0024</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6.4362</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-5.4338</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.578000000000001</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-4.496</v>
-      </c>
-      <c r="I26" t="n">
-        <v>6.073799999999998</v>
-      </c>
-      <c r="J26" t="n">
-        <v>12.6637</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-0.9176000000000002</v>
-      </c>
-      <c r="L26" t="n">
-        <v>13.5813</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-11.0858</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-3.5784</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-7.507200000000001</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-2.0549</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-10.274</v>
-      </c>
-      <c r="R26" t="n">
-        <v>8.219099999999999</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-1.0274</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-4.960100000000001</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.9326</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.506800000000001</v>
-      </c>
-      <c r="W26" t="n">
-        <v>9.006600000000001</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+        <v>-6.499999999999999</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
